--- a/naver-place-crawler/results_health/수영구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/수영구_헬스장.xlsx
@@ -421,18 +421,18 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>위드피트니스&amp;PT 남천점</t>
+          <t>벨로시티휘트니스&amp;PT 광안점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>with_namcheon@naver.com</t>
+          <t>velocity_gwangan@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1350-6707</t>
+          <t>0507-1401-6900</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 광남로 35 위드피트니스 4,5층</t>
+          <t>부산광역시 수영구 수영로 631 파스텔라 스튜디오 2, 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/with_namcheon</t>
+          <t>https://www.instagram.com/chelsea_gwangan/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>630</v>
+        <v>213</v>
       </c>
       <c r="Q2" t="n">
-        <v>1518</v>
+        <v>422</v>
       </c>
       <c r="R2" t="n">
-        <v>2148</v>
+        <v>635</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1838300399</t>
+          <t>36266433</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1838300399</t>
+          <t>https://m.place.naver.com/place/36266433</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>비해피휘트니스 광안역점</t>
+          <t>스탠다드짐 헬스&amp;PT 남천점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>aor403@naver.com</t>
+          <t>standardgym@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1363-2221</t>
+          <t>0507-1362-1827</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 장대골로 10 1층</t>
+          <t>부산광역시 수영구 황령대로 497 1층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/vhappy_fitness?igsh=MW5hcjJyZTdiaGd2Mw==</t>
+          <t>https://blog.naver.com/standardgym</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>622</v>
+        <v>166</v>
       </c>
       <c r="Q3" t="n">
-        <v>337</v>
+        <v>777</v>
       </c>
       <c r="R3" t="n">
-        <v>959</v>
+        <v>943</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1560721971</t>
+          <t>1575112833</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1560721971</t>
+          <t>https://m.place.naver.com/place/1575112833</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -812,10 +812,10 @@
         <v>410</v>
       </c>
       <c r="Q4" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="R4" t="n">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -846,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>달라스짐 더 프리미엄 헬스&amp;PT</t>
+          <t>비해피휘트니스 광안역점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dallasgympremium@naver.com</t>
+          <t>aor403@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1322-7591</t>
+          <t>0507-1363-2221</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 광안해변로 292 2층 달라스짐 더 프리미엄</t>
+          <t>부산광역시 수영구 장대골로 10 1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dallasgym_the_premium</t>
+          <t>https://www.instagram.com/vhappy_fitness?igsh=MW5hcjJyZTdiaGd2Mw==</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -894,7 +894,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>829</v>
+        <v>623</v>
       </c>
       <c r="Q5" t="n">
-        <v>1275</v>
+        <v>339</v>
       </c>
       <c r="R5" t="n">
-        <v>2104</v>
+        <v>962</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1792697479</t>
+          <t>1560721971</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1792697479</t>
+          <t>https://m.place.naver.com/place/1560721971</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -940,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>비해피휘트니스 수영점 헬스PT</t>
+          <t>정석피트니스 수영점 헬스 PT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>vitamin1448@naver.com</t>
+          <t>standardpt2@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>051-757-7575</t>
+          <t>0507-1364-4896</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로 641 2층 비해피휘트니스 수영점</t>
+          <t>부산광역시 수영구 수영로 701 선옥빌딩 2, 3층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/standardpt2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>425</v>
+        <v>477</v>
       </c>
       <c r="Q6" t="n">
-        <v>536</v>
+        <v>135</v>
       </c>
       <c r="R6" t="n">
-        <v>961</v>
+        <v>612</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1878819501</t>
+          <t>1050344461</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1878819501</t>
+          <t>https://m.place.naver.com/place/1050344461</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1034,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>정석피트니스 수영점 헬스 PT</t>
+          <t>비해피휘트니스 수영점 헬스PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>standardpt2@naver.com</t>
+          <t>vitamin1448@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1364-4896</t>
+          <t>051-757-7575</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로 701 선옥빌딩 2, 3층</t>
+          <t>부산광역시 수영구 수영로 641 2층 비해피휘트니스 수영점</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/standardpt2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1087,17 +1087,17 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>477</v>
+        <v>425</v>
       </c>
       <c r="Q7" t="n">
-        <v>135</v>
+        <v>538</v>
       </c>
       <c r="R7" t="n">
-        <v>612</v>
+        <v>963</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1050344461</t>
+          <t>1878819501</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1050344461</t>
+          <t>https://m.place.naver.com/place/1878819501</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1128,29 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>큐브휘트니스 수영점</t>
+          <t>버닝209 그룹PT 하이록스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kkddhh7336@naver.com</t>
+          <t>burning209@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1395-0251</t>
+          <t>0507-1315-9209</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로 668 화목오피스텔 4층</t>
+          <t>부산광역시 수영구 광남로 209 지하1층 BURNING209</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cube_suyeong</t>
+          <t>https://www.instagram.com/burning209_official</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>366</v>
+        <v>75</v>
       </c>
       <c r="Q8" t="n">
-        <v>414</v>
+        <v>108</v>
       </c>
       <c r="R8" t="n">
-        <v>780</v>
+        <v>183</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1620523545</t>
+          <t>1861353958</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1620523545</t>
+          <t>https://m.place.naver.com/place/1861353958</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1222,29 +1222,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>내셔널팀피트니스 헬스장 &amp; PT 수영점</t>
+          <t>바레피플&amp;88PT 수영역점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>awdxasd@naver.com</t>
+          <t>sukja7820@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0507-1392-8113</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로705번길 14 4층 내셔널팀 휘트니스 헬스장 수영점</t>
+          <t>부산 수영구 수영로 646 2층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ntf_suyeong</t>
+          <t>https://www.instagram.com/barrepeople_88pt/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>362</v>
+        <v>174</v>
       </c>
       <c r="Q9" t="n">
-        <v>354</v>
+        <v>12</v>
       </c>
       <c r="R9" t="n">
-        <v>716</v>
+        <v>186</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1290,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1886402536</t>
+          <t>1150292233</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1886402536</t>
+          <t>https://m.place.naver.com/place/1150292233</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1394,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1423,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로 577 11층</t>
+          <t>부산 수영구 수영로 577 11층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1452,10 +1448,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5646x2</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로618번길 4 성우이린타워 5층</t>
+          <t>부산 수영구 수영로618번길 4 성우이린타워 5층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1546,10 +1546,14 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wp7eiju</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1586,7 +1590,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
